--- a/Config/Datas/player_bag.xlsx
+++ b/Config/Datas/player_bag.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_bag" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="player_bag" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>EYCAttribute</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EYCAttribute 数值；0 表示无</t>
+          <t>增加该背包容量的 EYCAttribute；属性值会加到基础容量上</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -644,8 +644,10 @@
           <t>Grid</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MainBagSlots</t>
+        </is>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -674,8 +676,10 @@
           <t>Compact</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SecretBagSlots</t>
+        </is>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -704,8 +708,10 @@
           <t>Compact</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MindBagSlots</t>
+        </is>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -734,8 +740,10 @@
           <t>Compact</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ImportantBagSlots</t>
+        </is>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -764,8 +772,10 @@
           <t>Compact</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>8</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PlantBagSlots</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -799,8 +809,10 @@
           <t>Compact</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>9</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KeyBagSlots</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -834,8 +846,10 @@
           <t>Compact</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>10</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PotionBagSlots</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -869,8 +883,10 @@
           <t>Compact</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CommonStorageSlots</t>
+        </is>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -899,8 +915,10 @@
           <t>Compact</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FurnitureStorageSlots</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>

--- a/Config/Datas/player_bag.xlsx
+++ b/Config/Datas/player_bag.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,16 @@
           <t>gain_priority</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>weight_ratio</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>yc_weight_ratio_attr_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +529,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>EYCAttribute</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -571,6 +591,16 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -623,6 +653,16 @@
           <t>获得物品时的特殊包优先级；&lt;=0 不参与自动入包</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>负重折算</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>负重属性</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -654,6 +694,14 @@
       </c>
       <c r="J5" t="n">
         <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MainBagWeightRatio</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -687,6 +735,14 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
+      <c r="K6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>SecretBagWeightRatio</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -719,6 +775,14 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
+      <c r="K7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MindBagWeightRatio</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -751,6 +815,14 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
+      <c r="K8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ImportantBagWeightRatio</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -788,6 +860,14 @@
       <c r="J9" t="n">
         <v>10</v>
       </c>
+      <c r="K9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PlantBagWeightRatio</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -825,6 +905,14 @@
       <c r="J10" t="n">
         <v>20</v>
       </c>
+      <c r="K10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>KeyBagWeightRatio</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -862,6 +950,14 @@
       <c r="J11" t="n">
         <v>30</v>
       </c>
+      <c r="K11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PotionBagWeightRatio</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -894,6 +990,14 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -930,6 +1034,62 @@
       </c>
       <c r="J13" t="n">
         <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>大件包</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grid</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BigBagSlots</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Big</t>
+        </is>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>BigBagWeightRatio</t>
+        </is>
       </c>
     </row>
   </sheetData>
